--- a/簡易説明書.xlsx
+++ b/簡易説明書.xlsx
@@ -6514,22 +6514,22 @@
       <c r="H89" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J89" t="n">
+      <c r="J89" s="0" t="n">
         <v>92</v>
       </c>
-      <c r="K89" t="n">
+      <c r="K89" s="0" t="n">
         <v>6.1</v>
       </c>
-      <c r="L89" t="n">
-        <v>3</v>
-      </c>
-      <c r="M89" t="n">
+      <c r="L89" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="M89" s="0" t="n">
         <v>4.6</v>
       </c>
-      <c r="N89" t="n">
+      <c r="N89" s="0" t="n">
         <v>1.4</v>
       </c>
-      <c r="O89" t="n">
+      <c r="O89" s="0" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6557,22 +6557,22 @@
       <c r="H90" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J90" t="n">
+      <c r="J90" s="0" t="n">
         <v>141</v>
       </c>
-      <c r="K90" t="n">
+      <c r="K90" s="0" t="n">
         <v>6.7</v>
       </c>
-      <c r="L90" t="n">
+      <c r="L90" s="0" t="n">
         <v>3.1</v>
       </c>
-      <c r="M90" t="n">
+      <c r="M90" s="0" t="n">
         <v>5.6</v>
       </c>
-      <c r="N90" t="n">
+      <c r="N90" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O90" t="n">
+      <c r="O90" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6600,22 +6600,22 @@
       <c r="H91" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J91" t="n">
+      <c r="J91" s="0" t="n">
         <v>49</v>
       </c>
-      <c r="K91" t="n">
+      <c r="K91" s="0" t="n">
         <v>5.3</v>
       </c>
-      <c r="L91" t="n">
+      <c r="L91" s="0" t="n">
         <v>3.7</v>
       </c>
-      <c r="M91" t="n">
+      <c r="M91" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="N91" t="n">
+      <c r="N91" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="O91" t="n">
+      <c r="O91" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6643,22 +6643,22 @@
       <c r="H92" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J92" t="n">
+      <c r="J92" s="0" t="n">
         <v>147</v>
       </c>
-      <c r="K92" t="n">
+      <c r="K92" s="0" t="n">
         <v>6.3</v>
       </c>
-      <c r="L92" t="n">
+      <c r="L92" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="M92" t="n">
+      <c r="M92" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="N92" t="n">
+      <c r="N92" s="0" t="n">
         <v>1.9</v>
       </c>
-      <c r="O92" t="n">
+      <c r="O92" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6686,22 +6686,22 @@
       <c r="H93" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J93" t="n">
+      <c r="J93" s="0" t="n">
         <v>95</v>
       </c>
-      <c r="K93" t="n">
+      <c r="K93" s="0" t="n">
         <v>5.6</v>
       </c>
-      <c r="L93" t="n">
+      <c r="L93" s="0" t="n">
         <v>2.7</v>
       </c>
-      <c r="M93" t="n">
+      <c r="M93" s="0" t="n">
         <v>4.2</v>
       </c>
-      <c r="N93" t="n">
+      <c r="N93" s="0" t="n">
         <v>1.3</v>
       </c>
-      <c r="O93" t="n">
+      <c r="O93" s="0" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6729,22 +6729,22 @@
       <c r="H94" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J94" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K94" t="n">
+      <c r="K94" s="0" t="n">
         <v>4.6</v>
       </c>
-      <c r="L94" t="n">
+      <c r="L94" s="0" t="n">
         <v>3.1</v>
       </c>
-      <c r="M94" t="n">
+      <c r="M94" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="N94" t="n">
+      <c r="N94" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="O94" t="n">
+      <c r="O94" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6772,22 +6772,22 @@
       <c r="H95" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J95" s="0" t="n">
         <v>127</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K95" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="L95" t="n">
+      <c r="L95" s="0" t="n">
         <v>2.8</v>
       </c>
-      <c r="M95" t="n">
+      <c r="M95" s="0" t="n">
         <v>4.8</v>
       </c>
-      <c r="N95" t="n">
+      <c r="N95" s="0" t="n">
         <v>1.8</v>
       </c>
-      <c r="O95" t="n">
+      <c r="O95" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6815,22 +6815,22 @@
       <c r="H96" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J96" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K96" s="0" t="n">
         <v>5.7</v>
       </c>
-      <c r="L96" t="n">
+      <c r="L96" s="0" t="n">
         <v>3.8</v>
       </c>
-      <c r="M96" t="n">
+      <c r="M96" s="0" t="n">
         <v>1.7</v>
       </c>
-      <c r="N96" t="n">
+      <c r="N96" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="O96" t="n">
+      <c r="O96" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6858,22 +6858,22 @@
       <c r="H97" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J97" t="n">
+      <c r="J97" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="K97" t="n">
+      <c r="K97" s="0" t="n">
         <v>6.5</v>
       </c>
-      <c r="L97" t="n">
+      <c r="L97" s="0" t="n">
         <v>2.8</v>
       </c>
-      <c r="M97" t="n">
+      <c r="M97" s="0" t="n">
         <v>4.6</v>
       </c>
-      <c r="N97" t="n">
+      <c r="N97" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="O97" t="n">
+      <c r="O97" s="0" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6901,22 +6901,22 @@
       <c r="H98" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J98" t="n">
+      <c r="J98" s="0" t="n">
         <v>131</v>
       </c>
-      <c r="K98" t="n">
+      <c r="K98" s="0" t="n">
         <v>7.4</v>
       </c>
-      <c r="L98" t="n">
+      <c r="L98" s="0" t="n">
         <v>2.8</v>
       </c>
-      <c r="M98" t="n">
+      <c r="M98" s="0" t="n">
         <v>6.1</v>
       </c>
-      <c r="N98" t="n">
+      <c r="N98" s="0" t="n">
         <v>1.9</v>
       </c>
-      <c r="O98" t="n">
+      <c r="O98" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6944,22 +6944,22 @@
       <c r="H99" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J99" t="n">
+      <c r="J99" s="0" t="n">
         <v>112</v>
       </c>
-      <c r="K99" t="n">
+      <c r="K99" s="0" t="n">
         <v>6.4</v>
       </c>
-      <c r="L99" t="n">
+      <c r="L99" s="0" t="n">
         <v>2.7</v>
       </c>
-      <c r="M99" t="n">
+      <c r="M99" s="0" t="n">
         <v>5.3</v>
       </c>
-      <c r="N99" t="n">
+      <c r="N99" s="0" t="n">
         <v>1.9</v>
       </c>
-      <c r="O99" t="n">
+      <c r="O99" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6987,22 +6987,22 @@
       <c r="H100" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J100" t="n">
+      <c r="J100" s="0" t="n">
         <v>115</v>
       </c>
-      <c r="K100" t="n">
+      <c r="K100" s="0" t="n">
         <v>5.8</v>
       </c>
-      <c r="L100" t="n">
+      <c r="L100" s="0" t="n">
         <v>2.8</v>
       </c>
-      <c r="M100" t="n">
+      <c r="M100" s="0" t="n">
         <v>5.1</v>
       </c>
-      <c r="N100" t="n">
+      <c r="N100" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O100" t="n">
+      <c r="O100" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7030,22 +7030,22 @@
       <c r="H101" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J101" t="n">
+      <c r="J101" s="0" t="n">
         <v>79</v>
       </c>
-      <c r="K101" t="n">
+      <c r="K101" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="L101" t="n">
+      <c r="L101" s="0" t="n">
         <v>2.9</v>
       </c>
-      <c r="M101" t="n">
+      <c r="M101" s="0" t="n">
         <v>4.5</v>
       </c>
-      <c r="N101" t="n">
+      <c r="N101" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="O101" t="n">
+      <c r="O101" s="0" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7073,22 +7073,22 @@
       <c r="H102" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J102" t="n">
+      <c r="J102" s="0" t="n">
         <v>38</v>
       </c>
-      <c r="K102" t="n">
+      <c r="K102" s="0" t="n">
         <v>4.9</v>
       </c>
-      <c r="L102" t="n">
+      <c r="L102" s="0" t="n">
         <v>3.6</v>
       </c>
-      <c r="M102" t="n">
+      <c r="M102" s="0" t="n">
         <v>1.4</v>
       </c>
-      <c r="N102" t="n">
+      <c r="N102" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="O102" t="n">
+      <c r="O102" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7116,22 +7116,22 @@
       <c r="H103" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J103" t="n">
+      <c r="J103" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="K103" t="n">
+      <c r="K103" s="0" t="n">
         <v>4.4</v>
       </c>
-      <c r="L103" t="n">
+      <c r="L103" s="0" t="n">
         <v>2.9</v>
       </c>
-      <c r="M103" t="n">
+      <c r="M103" s="0" t="n">
         <v>1.4</v>
       </c>
-      <c r="N103" t="n">
+      <c r="N103" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="O103" t="n">
+      <c r="O103" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
       <c r="H104" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J104" t="n">
+      <c r="J104" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="K104" t="n">
+      <c r="K104" s="0" t="n">
         <v>5.7</v>
       </c>
-      <c r="L104" t="n">
+      <c r="L104" s="0" t="n">
         <v>2.8</v>
       </c>
-      <c r="M104" t="n">
+      <c r="M104" s="0" t="n">
         <v>4.1</v>
       </c>
-      <c r="N104" t="n">
+      <c r="N104" s="0" t="n">
         <v>1.3</v>
       </c>
-      <c r="O104" t="n">
+      <c r="O104" s="0" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7202,22 +7202,22 @@
       <c r="H105" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J105" t="n">
+      <c r="J105" s="0" t="n">
         <v>149</v>
       </c>
-      <c r="K105" t="n">
+      <c r="K105" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="L105" t="n">
+      <c r="L105" s="0" t="n">
         <v>3.4</v>
       </c>
-      <c r="M105" t="n">
+      <c r="M105" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="N105" t="n">
+      <c r="N105" s="0" t="n">
         <v>2.3</v>
       </c>
-      <c r="O105" t="n">
+      <c r="O105" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7245,22 +7245,22 @@
       <c r="H106" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J106" t="n">
+      <c r="J106" s="0" t="n">
         <v>146</v>
       </c>
-      <c r="K106" t="n">
+      <c r="K106" s="0" t="n">
         <v>6.7</v>
       </c>
-      <c r="L106" t="n">
-        <v>3</v>
-      </c>
-      <c r="M106" t="n">
+      <c r="L106" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="M106" s="0" t="n">
         <v>5.2</v>
       </c>
-      <c r="N106" t="n">
+      <c r="N106" s="0" t="n">
         <v>2.3</v>
       </c>
-      <c r="O106" t="n">
+      <c r="O106" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7288,22 +7288,22 @@
       <c r="H107" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J107" t="n">
+      <c r="J107" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="K107" t="n">
+      <c r="K107" s="0" t="n">
         <v>5.7</v>
       </c>
-      <c r="L107" t="n">
+      <c r="L107" s="0" t="n">
         <v>4.4</v>
       </c>
-      <c r="M107" t="n">
+      <c r="M107" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="N107" t="n">
+      <c r="N107" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="O107" t="n">
+      <c r="O107" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7331,22 +7331,22 @@
       <c r="H108" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J108" t="n">
+      <c r="J108" s="0" t="n">
         <v>67</v>
       </c>
-      <c r="K108" t="n">
+      <c r="K108" s="0" t="n">
         <v>5.6</v>
       </c>
-      <c r="L108" t="n">
-        <v>3</v>
-      </c>
-      <c r="M108" t="n">
+      <c r="L108" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="M108" s="0" t="n">
         <v>4.5</v>
       </c>
-      <c r="N108" t="n">
+      <c r="N108" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="O108" t="n">
+      <c r="O108" s="0" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7374,22 +7374,22 @@
       <c r="H109" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J109" t="n">
+      <c r="J109" s="0" t="n">
         <v>145</v>
       </c>
-      <c r="K109" t="n">
+      <c r="K109" s="0" t="n">
         <v>6.7</v>
       </c>
-      <c r="L109" t="n">
+      <c r="L109" s="0" t="n">
         <v>3.3</v>
       </c>
-      <c r="M109" t="n">
+      <c r="M109" s="0" t="n">
         <v>5.7</v>
       </c>
-      <c r="N109" t="n">
+      <c r="N109" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="O109" t="n">
+      <c r="O109" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7417,22 +7417,22 @@
       <c r="H110" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J110" t="n">
+      <c r="J110" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="K110" t="n">
+      <c r="K110" s="0" t="n">
         <v>4.3</v>
       </c>
-      <c r="L110" t="n">
-        <v>3</v>
-      </c>
-      <c r="M110" t="n">
+      <c r="L110" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="M110" s="0" t="n">
         <v>1.1</v>
       </c>
-      <c r="N110" t="n">
+      <c r="N110" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="O110" t="n">
+      <c r="O110" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7460,22 +7460,22 @@
       <c r="H111" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J111" t="n">
+      <c r="J111" s="0" t="n">
         <v>143</v>
       </c>
-      <c r="K111" t="n">
+      <c r="K111" s="0" t="n">
         <v>5.8</v>
       </c>
-      <c r="L111" t="n">
+      <c r="L111" s="0" t="n">
         <v>2.7</v>
       </c>
-      <c r="M111" t="n">
+      <c r="M111" s="0" t="n">
         <v>5.1</v>
       </c>
-      <c r="N111" t="n">
+      <c r="N111" s="0" t="n">
         <v>1.9</v>
       </c>
-      <c r="O111" t="n">
+      <c r="O111" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7503,22 +7503,22 @@
       <c r="H112" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J112" t="n">
-        <v>3</v>
-      </c>
-      <c r="K112" t="n">
+      <c r="J112" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K112" s="0" t="n">
         <v>4.7</v>
       </c>
-      <c r="L112" t="n">
+      <c r="L112" s="0" t="n">
         <v>3.2</v>
       </c>
-      <c r="M112" t="n">
+      <c r="M112" s="0" t="n">
         <v>1.3</v>
       </c>
-      <c r="N112" t="n">
+      <c r="N112" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="O112" t="n">
+      <c r="O112" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7546,22 +7546,22 @@
       <c r="H113" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J113" t="n">
+      <c r="J113" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="K113" t="n">
+      <c r="K113" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="L113" t="n">
+      <c r="L113" s="0" t="n">
         <v>3.3</v>
       </c>
-      <c r="M113" t="n">
+      <c r="M113" s="0" t="n">
         <v>1.4</v>
       </c>
-      <c r="N113" t="n">
+      <c r="N113" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="O113" t="n">
+      <c r="O113" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7589,22 +7589,22 @@
       <c r="H114" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J114" t="n">
+      <c r="J114" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="K114" t="n">
+      <c r="K114" s="0" t="n">
         <v>5.1</v>
       </c>
-      <c r="L114" t="n">
+      <c r="L114" s="0" t="n">
         <v>3.7</v>
       </c>
-      <c r="M114" t="n">
+      <c r="M114" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="N114" t="n">
+      <c r="N114" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="O114" t="n">
+      <c r="O114" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7632,22 +7632,22 @@
       <c r="H115" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J115" t="n">
+      <c r="J115" s="0" t="n">
         <v>128</v>
       </c>
-      <c r="K115" t="n">
+      <c r="K115" s="0" t="n">
         <v>6.1</v>
       </c>
-      <c r="L115" t="n">
-        <v>3</v>
-      </c>
-      <c r="M115" t="n">
+      <c r="L115" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="M115" s="0" t="n">
         <v>4.9</v>
       </c>
-      <c r="N115" t="n">
+      <c r="N115" s="0" t="n">
         <v>1.8</v>
       </c>
-      <c r="O115" t="n">
+      <c r="O115" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7675,22 +7675,22 @@
       <c r="H116" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J116" t="n">
+      <c r="J116" s="0" t="n">
         <v>107</v>
       </c>
-      <c r="K116" t="n">
+      <c r="K116" s="0" t="n">
         <v>4.9</v>
       </c>
-      <c r="L116" t="n">
+      <c r="L116" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="M116" t="n">
+      <c r="M116" s="0" t="n">
         <v>4.5</v>
       </c>
-      <c r="N116" t="n">
+      <c r="N116" s="0" t="n">
         <v>1.7</v>
       </c>
-      <c r="O116" t="n">
+      <c r="O116" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8882,11 +8882,7 @@
         <f>COUNTIF($P$9:$P$81,"TRUE")/COUNT($I$9:$I$81)</f>
         <v/>
       </c>
-      <c r="Q7" s="0" t="inlineStr">
-        <is>
-          <t>※これは出来すぎ</t>
-        </is>
-      </c>
+      <c r="Q7" s="0" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="0" t="inlineStr">
@@ -8946,26 +8942,26 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>0.961038961038961</v>
+        <v>0.9904761904761905</v>
       </c>
       <c r="E9" s="50" t="n"/>
       <c r="I9" s="0" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="L9" s="0" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="M9" s="0" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" s="12">
         <f>'アイリス(1)'!V12</f>
@@ -8978,22 +8974,22 @@
     </row>
     <row r="10">
       <c r="I10" s="0" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="L10" s="0" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="M10" s="0" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" s="12">
         <f>'アイリス(1)'!V13</f>
@@ -9016,19 +9012,19 @@
         </is>
       </c>
       <c r="I11" s="0" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="L11" s="0" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="M11" s="0" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N11" s="11" t="n">
         <v>1</v>
@@ -9063,10 +9059,10 @@
         </is>
       </c>
       <c r="I12" s="0" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="K12" s="0" t="n">
         <v>3.4</v>
@@ -9075,7 +9071,7 @@
         <v>1.5</v>
       </c>
       <c r="M12" s="0" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="N12" s="11" t="n">
         <v>1</v>
@@ -9094,7 +9090,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>0</v>
@@ -9103,22 +9099,22 @@
         <v>0</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="L13" s="0" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="M13" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N13" s="11" t="n">
         <v>1</v>
@@ -9140,28 +9136,28 @@
         <v>0</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="I14" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="I14" s="0" t="n">
-        <v>11</v>
-      </c>
       <c r="J14" s="0" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="L14" s="0" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M14" s="0" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="N14" s="11" t="n">
         <v>1</v>
@@ -9183,31 +9179,31 @@
         <v>0</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="L15" s="0" t="n">
-        <v>1.6</v>
+        <v>5.9</v>
       </c>
       <c r="M15" s="0" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O15" s="12">
         <f>'アイリス(1)'!V18</f>
@@ -9225,34 +9221,34 @@
         </is>
       </c>
       <c r="C16" s="0" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="J16" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" s="0" t="n">
         <v>4.8</v>
       </c>
-      <c r="K16" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" s="0" t="n">
-        <v>1.4</v>
-      </c>
       <c r="M16" s="0" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O16" s="12">
         <f>'アイリス(1)'!V19</f>
@@ -9265,22 +9261,22 @@
     </row>
     <row r="17">
       <c r="I17" s="0" t="n">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L17" s="0" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="M17" s="0" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="N17" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O17" s="12">
         <f>'アイリス(1)'!V20</f>
@@ -9303,22 +9299,22 @@
         </is>
       </c>
       <c r="I18" s="0" t="n">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K18" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L18" s="0" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="M18" s="0" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="N18" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O18" s="12">
         <f>'アイリス(1)'!V21</f>
@@ -9331,22 +9327,22 @@
     </row>
     <row r="19">
       <c r="I19" s="0" t="n">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K19" s="0" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="L19" s="0" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="M19" s="0" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="N19" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="12">
         <f>'アイリス(1)'!V22</f>
@@ -9373,22 +9369,22 @@
         <v>3</v>
       </c>
       <c r="I20" s="0" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="K20" s="0" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="L20" s="0" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="M20" s="0" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="N20" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" s="12">
         <f>'アイリス(1)'!V23</f>
@@ -9406,28 +9402,28 @@
         </is>
       </c>
       <c r="C21" s="0" t="n">
-        <v>0.298701298701298</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.35064935064935</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>0.35064935064935</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I21" s="0" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="K21" s="0" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L21" s="0" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="M21" s="0" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="N21" s="11" t="n">
         <v>1</v>
@@ -9443,22 +9439,22 @@
     </row>
     <row r="22">
       <c r="I22" s="0" t="n">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>4.6</v>
+        <v>6.9</v>
       </c>
       <c r="K22" s="0" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="L22" s="0" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="M22" s="0" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="N22" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O22" s="12">
         <f>'アイリス(1)'!V25</f>
@@ -9496,22 +9492,22 @@
         </is>
       </c>
       <c r="I23" s="0" t="n">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="K23" s="0" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="L23" s="0" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="M23" s="0" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="N23" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23" s="12">
         <f>'アイリス(1)'!V26</f>
@@ -9529,34 +9525,34 @@
         </is>
       </c>
       <c r="C24" s="0" t="n">
-        <v>4.85408682726872</v>
+        <v>6.606328834884184</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>5.49296207855806</v>
+        <v>7.133374303056966</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>-28.1277670727291</v>
+        <v>-35.8104998091945</v>
       </c>
       <c r="F24" s="0" t="n">
-        <v>-12.7693021013843</v>
+        <v>-22.10593632095443</v>
       </c>
       <c r="I24" s="0" t="n">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="J24" s="0" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="K24" s="0" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="L24" s="0" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="M24" s="0" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="N24" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O24" s="12">
         <f>'アイリス(1)'!V27</f>
@@ -9574,34 +9570,34 @@
         </is>
       </c>
       <c r="C25" s="0" t="n">
-        <v>-1.08045731675197</v>
+        <v>-1.269710622962055</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>-1.64676129965946</v>
+        <v>-2.400681437299602</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>6.50197561273009</v>
+        <v>8.953247758426885</v>
       </c>
       <c r="F25" s="0" t="n">
-        <v>1.19623146839658</v>
+        <v>4.240076312115054</v>
       </c>
       <c r="I25" s="0" t="n">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="J25" s="0" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="K25" s="0" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="L25" s="0" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="M25" s="0" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="N25" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O25" s="12">
         <f>'アイリス(1)'!V28</f>
@@ -9619,31 +9615,31 @@
         </is>
       </c>
       <c r="C26" s="0" t="n">
-        <v>-3.05450553610652</v>
+        <v>-5.336618211922159</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>-3.03242861911222</v>
+        <v>-4.732692865757328</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>17.4587148566316</v>
+        <v>26.85725205076766</v>
       </c>
       <c r="F26" s="0" t="n">
-        <v>9.68132217352348</v>
+        <v>17.86586000883929</v>
       </c>
       <c r="I26" s="0" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J26" s="0" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="K26" s="0" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L26" s="0" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="M26" s="0" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N26" s="11" t="n">
         <v>1</v>
@@ -9659,16 +9655,16 @@
     </row>
     <row r="27">
       <c r="I27" s="0" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J27" s="0" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="K27" s="0" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="L27" s="0" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="M27" s="0" t="n">
         <v>0.2</v>
@@ -9697,16 +9693,16 @@
         </is>
       </c>
       <c r="I28" s="0" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J28" s="0" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="K28" s="0" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="L28" s="0" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="M28" s="0" t="n">
         <v>0.2</v>
@@ -9730,19 +9726,19 @@
         </is>
       </c>
       <c r="C29" s="0" t="n">
-        <v>-29.3579483208231</v>
+        <v>-38.49158454214044</v>
       </c>
       <c r="I29" s="0" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J29" s="0" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K29" s="0" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="L29" s="0" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="M29" s="0" t="n">
         <v>0.2</v>
@@ -9766,25 +9762,25 @@
         </is>
       </c>
       <c r="C30" s="0" t="n">
-        <v>-2.33783105196003</v>
+        <v>-3.465114496313972</v>
       </c>
       <c r="I30" s="0" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="J30" s="0" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="K30" s="0" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="L30" s="0" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="M30" s="0" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="N30" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="12">
         <f>'アイリス(1)'!V33</f>
@@ -9802,19 +9798,19 @@
         </is>
       </c>
       <c r="C31" s="0" t="n">
-        <v>-13.3570202044428</v>
+        <v>-22.82079047689671</v>
       </c>
       <c r="I31" s="0" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="J31" s="0" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="K31" s="0" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="L31" s="0" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="M31" s="0" t="n">
         <v>0.2</v>
@@ -9833,22 +9829,22 @@
     </row>
     <row r="32">
       <c r="I32" s="0" t="n">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="J32" s="0" t="n">
-        <v>5.1</v>
+        <v>6.3</v>
       </c>
       <c r="K32" s="0" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="L32" s="0" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="M32" s="0" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="N32" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O32" s="12">
         <f>'アイリス(1)'!V35</f>
@@ -9886,22 +9882,22 @@
         </is>
       </c>
       <c r="I33" s="0" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="J33" s="0" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="K33" s="0" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="L33" s="0" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="M33" s="0" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="N33" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" s="12">
         <f>'アイリス(1)'!V36</f>
@@ -9919,28 +9915,28 @@
         </is>
       </c>
       <c r="C34" s="0" t="n">
-        <v>5.86103896103896</v>
+        <v>5.804761904761905</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>2.99220779220779</v>
+        <v>3.043809523809523</v>
       </c>
       <c r="E34" s="0" t="n">
-        <v>3.87792207792207</v>
+        <v>3.750476190476191</v>
       </c>
       <c r="F34" s="0" t="n">
-        <v>1.25844155844155</v>
+        <v>1.205714285714286</v>
       </c>
       <c r="I34" s="0" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="J34" s="0" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K34" s="0" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L34" s="0" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M34" s="0" t="n">
         <v>0.2</v>
@@ -9959,16 +9955,16 @@
     </row>
     <row r="35">
       <c r="I35" s="0" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="J35" s="0" t="n">
         <v>5</v>
       </c>
       <c r="K35" s="0" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L35" s="0" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M35" s="0" t="n">
         <v>0.2</v>
@@ -10012,22 +10008,22 @@
         </is>
       </c>
       <c r="I36" s="0" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="J36" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K36" s="0" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="L36" s="0" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="M36" s="0" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="N36" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O36" s="12">
         <f>'アイリス(1)'!V39</f>
@@ -10045,34 +10041,34 @@
         </is>
       </c>
       <c r="C37" s="0" t="n">
-        <v>0.74289762185866</v>
+        <v>0.6360725623582766</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>0.168770450328891</v>
+        <v>0.1923664399092971</v>
       </c>
       <c r="E37" s="0" t="n">
-        <v>2.9513307471749</v>
+        <v>2.97754739229025</v>
       </c>
       <c r="F37" s="0" t="n">
-        <v>0.559052116714454</v>
+        <v>0.5744435374149658</v>
       </c>
       <c r="I37" s="0" t="n">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="J37" s="0" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="K37" s="0" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="L37" s="0" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="M37" s="0" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O37" s="12">
         <f>'アイリス(1)'!V40</f>
@@ -10085,22 +10081,22 @@
     </row>
     <row r="38">
       <c r="I38" s="0" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="J38" s="0" t="n">
-        <v>6.9</v>
+        <v>4.5</v>
       </c>
       <c r="K38" s="0" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="L38" s="0" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="M38" s="0" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O38" s="12">
         <f>'アイリス(1)'!V41</f>
@@ -10118,22 +10114,22 @@
         </is>
       </c>
       <c r="I39" s="0" t="n">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="J39" s="0" t="n">
-        <v>6.3</v>
+        <v>7.7</v>
       </c>
       <c r="K39" s="0" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="L39" s="0" t="n">
-        <v>4.7</v>
+        <v>6.7</v>
       </c>
       <c r="M39" s="0" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O39" s="12">
         <f>'アイリス(1)'!V42</f>
@@ -10161,19 +10157,19 @@
         </is>
       </c>
       <c r="I40" s="0" t="n">
-        <v>60</v>
+        <v>134</v>
       </c>
       <c r="J40" s="0" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="K40" s="0" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="L40" s="0" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="M40" s="0" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="N40" s="11" t="n">
         <v>2</v>
@@ -10192,26 +10188,26 @@
         <v>1</v>
       </c>
       <c r="C41" s="0" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>0.36986301369863</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F41" s="50" t="n"/>
       <c r="I41" s="0" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="J41" s="0" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="K41" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L41" s="0" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="M41" s="0" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="N41" s="11" t="n">
         <v>2</v>
@@ -10230,29 +10226,29 @@
         <v>2</v>
       </c>
       <c r="C42" s="0" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>0.315068493150684</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F42" s="50" t="n"/>
       <c r="I42" s="0" t="n">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="J42" s="0" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="K42" s="0" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="L42" s="0" t="n">
-        <v>4</v>
+        <v>6.9</v>
       </c>
       <c r="M42" s="0" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="N42" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O42" s="12">
         <f>'アイリス(1)'!V45</f>
@@ -10268,29 +10264,29 @@
         <v>3</v>
       </c>
       <c r="C43" s="0" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>0.315068493150684</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F43" s="50" t="n"/>
       <c r="I43" s="0" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="J43" s="0" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="K43" s="0" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="L43" s="0" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="M43" s="0" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="N43" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O43" s="12">
         <f>'アイリス(1)'!V46</f>
@@ -10308,26 +10304,26 @@
         </is>
       </c>
       <c r="C44" s="0" t="n">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D44" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="50" t="n"/>
       <c r="I44" s="0" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J44" s="0" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="K44" s="0" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="L44" s="0" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="M44" s="0" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N44" s="11" t="n">
         <v>2</v>
@@ -10343,19 +10339,19 @@
     </row>
     <row r="45">
       <c r="I45" s="0" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="J45" s="0" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K45" s="0" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="L45" s="0" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="M45" s="0" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N45" s="11" t="n">
         <v>2</v>
@@ -10371,22 +10367,22 @@
     </row>
     <row r="46">
       <c r="I46" s="0" t="n">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="J46" s="0" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K46" s="0" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L46" s="0" t="n">
         <v>6.1</v>
       </c>
-      <c r="K46" s="0" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L46" s="0" t="n">
-        <v>4</v>
-      </c>
       <c r="M46" s="0" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="N46" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O46" s="12">
         <f>'アイリス(1)'!V49</f>
@@ -10399,19 +10395,19 @@
     </row>
     <row r="47">
       <c r="I47" s="0" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J47" s="0" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="K47" s="0" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="L47" s="0" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="M47" s="0" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="N47" s="11" t="n">
         <v>2</v>
@@ -10427,22 +10423,22 @@
     </row>
     <row r="48">
       <c r="I48" s="0" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="J48" s="0" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="K48" s="0" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="L48" s="0" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="M48" s="0" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="N48" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O48" s="12">
         <f>'アイリス(1)'!V51</f>
@@ -10455,19 +10451,19 @@
     </row>
     <row r="49">
       <c r="I49" s="0" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J49" s="0" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="K49" s="0" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="L49" s="0" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="M49" s="0" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="N49" s="11" t="n">
         <v>2</v>
@@ -10511,22 +10507,22 @@
     </row>
     <row r="51">
       <c r="I51" s="0" t="n">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="J51" s="0" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="K51" s="0" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="L51" s="0" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="M51" s="0" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="N51" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O51" s="12">
         <f>'アイリス(1)'!V54</f>
@@ -10539,16 +10535,16 @@
     </row>
     <row r="52">
       <c r="I52" s="0" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="J52" s="0" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K52" s="0" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="L52" s="0" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M52" s="0" t="n">
         <v>1.3</v>
@@ -10567,22 +10563,22 @@
     </row>
     <row r="53">
       <c r="I53" s="0" t="n">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>5.5</v>
+        <v>7.9</v>
       </c>
       <c r="K53" s="0" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="L53" s="0" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="M53" s="0" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N53" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O53" s="12">
         <f>'アイリス(1)'!V56</f>

--- a/簡易説明書.xlsx
+++ b/簡易説明書.xlsx
@@ -10,7 +10,6 @@
     <sheet name="検証⇒" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="アイリス(1)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="アイリス(2)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="アイリス_再検証" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -4652,24 +4651,12 @@
       <c r="O57" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="R57" s="1" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="S57" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="T57" s="1" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U57" s="1" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V57" s="10" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q57" s="1" t="n"/>
+      <c r="R57" s="1" t="n"/>
+      <c r="S57" s="1" t="n"/>
+      <c r="T57" s="1" t="n"/>
+      <c r="U57" s="1" t="n"/>
+      <c r="V57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="B58" s="1" t="n">
@@ -4713,24 +4700,12 @@
       <c r="O58" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q58" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="R58" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="S58" s="1" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T58" s="1" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U58" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V58" s="10" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q58" s="1" t="n"/>
+      <c r="R58" s="1" t="n"/>
+      <c r="S58" s="1" t="n"/>
+      <c r="T58" s="1" t="n"/>
+      <c r="U58" s="1" t="n"/>
+      <c r="V58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="B59" s="1" t="n">
@@ -4774,24 +4749,12 @@
       <c r="O59" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Q59" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="R59" s="1" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="S59" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="T59" s="1" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U59" s="1" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V59" s="10" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q59" s="1" t="n"/>
+      <c r="R59" s="1" t="n"/>
+      <c r="S59" s="1" t="n"/>
+      <c r="T59" s="1" t="n"/>
+      <c r="U59" s="1" t="n"/>
+      <c r="V59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="B60" s="1" t="n">
@@ -4835,24 +4798,12 @@
       <c r="O60" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="R60" s="1" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="S60" s="1" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T60" s="1" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U60" s="1" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V60" s="10" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q60" s="1" t="n"/>
+      <c r="R60" s="1" t="n"/>
+      <c r="S60" s="1" t="n"/>
+      <c r="T60" s="1" t="n"/>
+      <c r="U60" s="1" t="n"/>
+      <c r="V60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="B61" s="1" t="n">
@@ -4896,24 +4847,12 @@
       <c r="O61" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q61" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="R61" s="1" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="S61" s="1" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T61" s="1" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U61" s="1" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V61" s="10" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q61" s="1" t="n"/>
+      <c r="R61" s="1" t="n"/>
+      <c r="S61" s="1" t="n"/>
+      <c r="T61" s="1" t="n"/>
+      <c r="U61" s="1" t="n"/>
+      <c r="V61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="1" t="n">
@@ -4957,24 +4896,12 @@
       <c r="O62" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" s="1" t="n">
-        <v>102</v>
-      </c>
-      <c r="R62" s="1" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="S62" s="1" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T62" s="1" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="U62" s="1" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V62" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q62" s="1" t="n"/>
+      <c r="R62" s="1" t="n"/>
+      <c r="S62" s="1" t="n"/>
+      <c r="T62" s="1" t="n"/>
+      <c r="U62" s="1" t="n"/>
+      <c r="V62" s="10" t="n"/>
     </row>
     <row r="63">
       <c r="B63" s="1" t="n">
@@ -5018,24 +4945,12 @@
       <c r="O63" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q63" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="R63" s="1" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="S63" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="T63" s="1" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="U63" s="1" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V63" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q63" s="1" t="n"/>
+      <c r="R63" s="1" t="n"/>
+      <c r="S63" s="1" t="n"/>
+      <c r="T63" s="1" t="n"/>
+      <c r="U63" s="1" t="n"/>
+      <c r="V63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="1" t="n">
@@ -5079,24 +4994,12 @@
       <c r="O64" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q64" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="R64" s="1" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="S64" s="1" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T64" s="1" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="U64" s="1" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V64" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q64" s="1" t="n"/>
+      <c r="R64" s="1" t="n"/>
+      <c r="S64" s="1" t="n"/>
+      <c r="T64" s="1" t="n"/>
+      <c r="U64" s="1" t="n"/>
+      <c r="V64" s="10" t="n"/>
     </row>
     <row r="65">
       <c r="B65" s="1" t="n">
@@ -5140,24 +5043,12 @@
       <c r="O65" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q65" s="1" t="n">
-        <v>110</v>
-      </c>
-      <c r="R65" s="1" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="S65" s="1" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T65" s="1" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="U65" s="1" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V65" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q65" s="1" t="n"/>
+      <c r="R65" s="1" t="n"/>
+      <c r="S65" s="1" t="n"/>
+      <c r="T65" s="1" t="n"/>
+      <c r="U65" s="1" t="n"/>
+      <c r="V65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="1" t="n">
@@ -5201,24 +5092,12 @@
       <c r="O66" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" s="1" t="n">
-        <v>111</v>
-      </c>
-      <c r="R66" s="1" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="S66" s="1" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T66" s="1" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="U66" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="V66" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q66" s="1" t="n"/>
+      <c r="R66" s="1" t="n"/>
+      <c r="S66" s="1" t="n"/>
+      <c r="T66" s="1" t="n"/>
+      <c r="U66" s="1" t="n"/>
+      <c r="V66" s="10" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="1" t="n">
@@ -5262,24 +5141,12 @@
       <c r="O67" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q67" s="1" t="n">
-        <v>114</v>
-      </c>
-      <c r="R67" s="1" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="S67" s="1" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T67" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="U67" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="V67" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q67" s="1" t="n"/>
+      <c r="R67" s="1" t="n"/>
+      <c r="S67" s="1" t="n"/>
+      <c r="T67" s="1" t="n"/>
+      <c r="U67" s="1" t="n"/>
+      <c r="V67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="1" t="n">
@@ -5323,24 +5190,12 @@
       <c r="O68" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Q68" s="1" t="n">
-        <v>118</v>
-      </c>
-      <c r="R68" s="1" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="S68" s="1" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T68" s="1" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="U68" s="1" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V68" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q68" s="1" t="n"/>
+      <c r="R68" s="1" t="n"/>
+      <c r="S68" s="1" t="n"/>
+      <c r="T68" s="1" t="n"/>
+      <c r="U68" s="1" t="n"/>
+      <c r="V68" s="10" t="n"/>
     </row>
     <row r="69">
       <c r="B69" s="1" t="n">
@@ -5384,24 +5239,12 @@
       <c r="O69" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q69" s="1" t="n">
-        <v>119</v>
-      </c>
-      <c r="R69" s="1" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="S69" s="1" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T69" s="1" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="U69" s="1" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V69" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q69" s="1" t="n"/>
+      <c r="R69" s="1" t="n"/>
+      <c r="S69" s="1" t="n"/>
+      <c r="T69" s="1" t="n"/>
+      <c r="U69" s="1" t="n"/>
+      <c r="V69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="B70" s="1" t="n">
@@ -5445,24 +5288,12 @@
       <c r="O70" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" s="1" t="n">
-        <v>124</v>
-      </c>
-      <c r="R70" s="1" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="S70" s="1" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T70" s="1" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="U70" s="1" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V70" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q70" s="1" t="n"/>
+      <c r="R70" s="1" t="n"/>
+      <c r="S70" s="1" t="n"/>
+      <c r="T70" s="1" t="n"/>
+      <c r="U70" s="1" t="n"/>
+      <c r="V70" s="10" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="1" t="n">
@@ -5506,24 +5337,12 @@
       <c r="O71" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q71" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="R71" s="1" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="S71" s="1" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T71" s="1" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="U71" s="1" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V71" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q71" s="1" t="n"/>
+      <c r="R71" s="1" t="n"/>
+      <c r="S71" s="1" t="n"/>
+      <c r="T71" s="1" t="n"/>
+      <c r="U71" s="1" t="n"/>
+      <c r="V71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="B72" s="1" t="n">
@@ -5567,24 +5386,12 @@
       <c r="O72" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q72" s="1" t="n">
-        <v>126</v>
-      </c>
-      <c r="R72" s="1" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="S72" s="1" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T72" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="U72" s="1" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V72" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q72" s="1" t="n"/>
+      <c r="R72" s="1" t="n"/>
+      <c r="S72" s="1" t="n"/>
+      <c r="T72" s="1" t="n"/>
+      <c r="U72" s="1" t="n"/>
+      <c r="V72" s="10" t="n"/>
     </row>
     <row r="73">
       <c r="B73" s="1" t="n">
@@ -5628,24 +5435,12 @@
       <c r="O73" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q73" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="R73" s="1" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="S73" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="T73" s="1" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="U73" s="1" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V73" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q73" s="1" t="n"/>
+      <c r="R73" s="1" t="n"/>
+      <c r="S73" s="1" t="n"/>
+      <c r="T73" s="1" t="n"/>
+      <c r="U73" s="1" t="n"/>
+      <c r="V73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="B74" s="1" t="n">
@@ -5689,24 +5484,12 @@
       <c r="O74" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q74" s="1" t="n">
-        <v>129</v>
-      </c>
-      <c r="R74" s="1" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="S74" s="1" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T74" s="1" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="U74" s="1" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V74" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q74" s="1" t="n"/>
+      <c r="R74" s="1" t="n"/>
+      <c r="S74" s="1" t="n"/>
+      <c r="T74" s="1" t="n"/>
+      <c r="U74" s="1" t="n"/>
+      <c r="V74" s="10" t="n"/>
     </row>
     <row r="75">
       <c r="B75" s="1" t="n">
@@ -5750,24 +5533,12 @@
       <c r="O75" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q75" s="1" t="n">
-        <v>131</v>
-      </c>
-      <c r="R75" s="1" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="S75" s="1" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T75" s="1" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="U75" s="1" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V75" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q75" s="1" t="n"/>
+      <c r="R75" s="1" t="n"/>
+      <c r="S75" s="1" t="n"/>
+      <c r="T75" s="1" t="n"/>
+      <c r="U75" s="1" t="n"/>
+      <c r="V75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="B76" s="1" t="n">
@@ -5811,24 +5582,12 @@
       <c r="O76" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q76" s="1" t="n">
-        <v>133</v>
-      </c>
-      <c r="R76" s="1" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="S76" s="1" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T76" s="1" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="U76" s="1" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V76" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q76" s="1" t="n"/>
+      <c r="R76" s="1" t="n"/>
+      <c r="S76" s="1" t="n"/>
+      <c r="T76" s="1" t="n"/>
+      <c r="U76" s="1" t="n"/>
+      <c r="V76" s="10" t="n"/>
     </row>
     <row r="77">
       <c r="B77" s="1" t="n">
@@ -5872,24 +5631,12 @@
       <c r="O77" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Q77" s="1" t="n">
-        <v>135</v>
-      </c>
-      <c r="R77" s="1" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="S77" s="1" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T77" s="1" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="U77" s="1" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V77" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q77" s="1" t="n"/>
+      <c r="R77" s="1" t="n"/>
+      <c r="S77" s="1" t="n"/>
+      <c r="T77" s="1" t="n"/>
+      <c r="U77" s="1" t="n"/>
+      <c r="V77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="B78" s="1" t="n">
@@ -5933,24 +5680,12 @@
       <c r="O78" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" s="1" t="n">
-        <v>137</v>
-      </c>
-      <c r="R78" s="1" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="S78" s="1" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T78" s="1" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="U78" s="1" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V78" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q78" s="1" t="n"/>
+      <c r="R78" s="1" t="n"/>
+      <c r="S78" s="1" t="n"/>
+      <c r="T78" s="1" t="n"/>
+      <c r="U78" s="1" t="n"/>
+      <c r="V78" s="10" t="n"/>
     </row>
     <row r="79">
       <c r="B79" s="1" t="n">
@@ -5994,24 +5729,12 @@
       <c r="O79" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Q79" s="1" t="n">
-        <v>138</v>
-      </c>
-      <c r="R79" s="1" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="S79" s="1" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T79" s="1" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U79" s="1" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V79" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q79" s="1" t="n"/>
+      <c r="R79" s="1" t="n"/>
+      <c r="S79" s="1" t="n"/>
+      <c r="T79" s="1" t="n"/>
+      <c r="U79" s="1" t="n"/>
+      <c r="V79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="B80" s="1" t="n">
@@ -6055,24 +5778,12 @@
       <c r="O80" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q80" s="1" t="n">
-        <v>139</v>
-      </c>
-      <c r="R80" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="S80" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="T80" s="1" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U80" s="1" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V80" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q80" s="1" t="n"/>
+      <c r="R80" s="1" t="n"/>
+      <c r="S80" s="1" t="n"/>
+      <c r="T80" s="1" t="n"/>
+      <c r="U80" s="1" t="n"/>
+      <c r="V80" s="10" t="n"/>
     </row>
     <row r="81">
       <c r="B81" s="1" t="n">
@@ -6116,24 +5827,12 @@
       <c r="O81" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q81" s="1" t="n">
-        <v>142</v>
-      </c>
-      <c r="R81" s="1" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="S81" s="1" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T81" s="1" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="U81" s="1" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V81" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q81" s="1" t="n"/>
+      <c r="R81" s="1" t="n"/>
+      <c r="S81" s="1" t="n"/>
+      <c r="T81" s="1" t="n"/>
+      <c r="U81" s="1" t="n"/>
+      <c r="V81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="B82" s="1" t="n">
@@ -6177,24 +5876,12 @@
       <c r="O82" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Q82" s="1" t="n">
-        <v>144</v>
-      </c>
-      <c r="R82" s="1" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="S82" s="1" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T82" s="1" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="U82" s="1" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V82" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q82" s="1" t="n"/>
+      <c r="R82" s="1" t="n"/>
+      <c r="S82" s="1" t="n"/>
+      <c r="T82" s="1" t="n"/>
+      <c r="U82" s="1" t="n"/>
+      <c r="V82" s="10" t="n"/>
     </row>
     <row r="83">
       <c r="B83" s="1" t="n">
@@ -6238,24 +5925,12 @@
       <c r="O83" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q83" s="1" t="n">
-        <v>149</v>
-      </c>
-      <c r="R83" s="1" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="S83" s="1" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T83" s="1" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="U83" s="1" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V83" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q83" s="1" t="n"/>
+      <c r="R83" s="1" t="n"/>
+      <c r="S83" s="1" t="n"/>
+      <c r="T83" s="1" t="n"/>
+      <c r="U83" s="1" t="n"/>
+      <c r="V83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="B84" s="1" t="n">
@@ -6299,24 +5974,12 @@
       <c r="O84" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Q84" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="R84" s="1" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="S84" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="T84" s="1" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="U84" s="1" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V84" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q84" s="1" t="n"/>
+      <c r="R84" s="1" t="n"/>
+      <c r="S84" s="1" t="n"/>
+      <c r="T84" s="1" t="n"/>
+      <c r="U84" s="1" t="n"/>
+      <c r="V84" s="10" t="n"/>
     </row>
     <row r="85">
       <c r="B85" s="1" t="n">
@@ -10590,1012 +10253,286 @@
       </c>
     </row>
     <row r="54">
-      <c r="I54" s="0" t="n">
-        <v>92</v>
-      </c>
-      <c r="J54" s="0" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K54" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="L54" s="0" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M54" s="0" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N54" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O54" s="12">
-        <f>'アイリス(1)'!V57</f>
-        <v/>
-      </c>
-      <c r="P54" s="0">
-        <f>O54=N54</f>
-        <v/>
-      </c>
+      <c r="I54" s="0" t="n"/>
+      <c r="J54" s="0" t="n"/>
+      <c r="K54" s="0" t="n"/>
+      <c r="L54" s="0" t="n"/>
+      <c r="M54" s="0" t="n"/>
+      <c r="N54" s="11" t="n"/>
+      <c r="O54" s="12" t="n"/>
+      <c r="P54" s="0" t="n"/>
     </row>
     <row r="55">
-      <c r="I55" s="0" t="n">
-        <v>94</v>
-      </c>
-      <c r="J55" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="K55" s="0" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L55" s="0" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M55" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O55" s="12">
-        <f>'アイリス(1)'!V58</f>
-        <v/>
-      </c>
-      <c r="P55" s="0">
-        <f>O55=N55</f>
-        <v/>
-      </c>
+      <c r="I55" s="0" t="n"/>
+      <c r="J55" s="0" t="n"/>
+      <c r="K55" s="0" t="n"/>
+      <c r="L55" s="0" t="n"/>
+      <c r="M55" s="0" t="n"/>
+      <c r="N55" s="11" t="n"/>
+      <c r="O55" s="12" t="n"/>
+      <c r="P55" s="0" t="n"/>
     </row>
     <row r="56">
-      <c r="I56" s="0" t="n">
-        <v>96</v>
-      </c>
-      <c r="J56" s="0" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K56" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="L56" s="0" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M56" s="0" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N56" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O56" s="12">
-        <f>'アイリス(1)'!V59</f>
-        <v/>
-      </c>
-      <c r="P56" s="0">
-        <f>O56=N56</f>
-        <v/>
-      </c>
+      <c r="I56" s="0" t="n"/>
+      <c r="J56" s="0" t="n"/>
+      <c r="K56" s="0" t="n"/>
+      <c r="L56" s="0" t="n"/>
+      <c r="M56" s="0" t="n"/>
+      <c r="N56" s="11" t="n"/>
+      <c r="O56" s="12" t="n"/>
+      <c r="P56" s="0" t="n"/>
     </row>
     <row r="57">
-      <c r="I57" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="J57" s="0" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K57" s="0" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L57" s="0" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M57" s="0" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N57" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O57" s="12">
-        <f>'アイリス(1)'!V60</f>
-        <v/>
-      </c>
-      <c r="P57" s="0">
-        <f>O57=N57</f>
-        <v/>
-      </c>
+      <c r="I57" s="0" t="n"/>
+      <c r="J57" s="0" t="n"/>
+      <c r="K57" s="0" t="n"/>
+      <c r="L57" s="0" t="n"/>
+      <c r="M57" s="0" t="n"/>
+      <c r="N57" s="11" t="n"/>
+      <c r="O57" s="12" t="n"/>
+      <c r="P57" s="0" t="n"/>
     </row>
     <row r="58">
-      <c r="I58" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="J58" s="0" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K58" s="0" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L58" s="0" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M58" s="0" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N58" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O58" s="12">
-        <f>'アイリス(1)'!V61</f>
-        <v/>
-      </c>
-      <c r="P58" s="0">
-        <f>O58=N58</f>
-        <v/>
-      </c>
+      <c r="I58" s="0" t="n"/>
+      <c r="J58" s="0" t="n"/>
+      <c r="K58" s="0" t="n"/>
+      <c r="L58" s="0" t="n"/>
+      <c r="M58" s="0" t="n"/>
+      <c r="N58" s="11" t="n"/>
+      <c r="O58" s="12" t="n"/>
+      <c r="P58" s="0" t="n"/>
     </row>
     <row r="59">
-      <c r="I59" s="0" t="n">
-        <v>102</v>
-      </c>
-      <c r="J59" s="0" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K59" s="0" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L59" s="0" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M59" s="0" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N59" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O59" s="12">
-        <f>'アイリス(1)'!V62</f>
-        <v/>
-      </c>
-      <c r="P59" s="0">
-        <f>O59=N59</f>
-        <v/>
-      </c>
+      <c r="I59" s="0" t="n"/>
+      <c r="J59" s="0" t="n"/>
+      <c r="K59" s="0" t="n"/>
+      <c r="L59" s="0" t="n"/>
+      <c r="M59" s="0" t="n"/>
+      <c r="N59" s="11" t="n"/>
+      <c r="O59" s="12" t="n"/>
+      <c r="P59" s="0" t="n"/>
     </row>
     <row r="60">
-      <c r="I60" s="0" t="n">
-        <v>103</v>
-      </c>
-      <c r="J60" s="0" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K60" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="L60" s="0" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M60" s="0" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N60" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O60" s="12">
-        <f>'アイリス(1)'!V63</f>
-        <v/>
-      </c>
-      <c r="P60" s="0">
-        <f>O60=N60</f>
-        <v/>
-      </c>
+      <c r="I60" s="0" t="n"/>
+      <c r="J60" s="0" t="n"/>
+      <c r="K60" s="0" t="n"/>
+      <c r="L60" s="0" t="n"/>
+      <c r="M60" s="0" t="n"/>
+      <c r="N60" s="11" t="n"/>
+      <c r="O60" s="12" t="n"/>
+      <c r="P60" s="0" t="n"/>
     </row>
     <row r="61">
-      <c r="I61" s="0" t="n">
-        <v>104</v>
-      </c>
-      <c r="J61" s="0" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K61" s="0" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L61" s="0" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M61" s="0" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N61" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O61" s="12">
-        <f>'アイリス(1)'!V64</f>
-        <v/>
-      </c>
-      <c r="P61" s="0">
-        <f>O61=N61</f>
-        <v/>
-      </c>
+      <c r="I61" s="0" t="n"/>
+      <c r="J61" s="0" t="n"/>
+      <c r="K61" s="0" t="n"/>
+      <c r="L61" s="0" t="n"/>
+      <c r="M61" s="0" t="n"/>
+      <c r="N61" s="11" t="n"/>
+      <c r="O61" s="12" t="n"/>
+      <c r="P61" s="0" t="n"/>
     </row>
     <row r="62">
-      <c r="I62" s="0" t="n">
-        <v>110</v>
-      </c>
-      <c r="J62" s="0" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K62" s="0" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L62" s="0" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M62" s="0" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N62" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O62" s="12">
-        <f>'アイリス(1)'!V65</f>
-        <v/>
-      </c>
-      <c r="P62" s="0">
-        <f>O62=N62</f>
-        <v/>
-      </c>
+      <c r="I62" s="0" t="n"/>
+      <c r="J62" s="0" t="n"/>
+      <c r="K62" s="0" t="n"/>
+      <c r="L62" s="0" t="n"/>
+      <c r="M62" s="0" t="n"/>
+      <c r="N62" s="11" t="n"/>
+      <c r="O62" s="12" t="n"/>
+      <c r="P62" s="0" t="n"/>
     </row>
     <row r="63">
-      <c r="I63" s="0" t="n">
-        <v>111</v>
-      </c>
-      <c r="J63" s="0" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K63" s="0" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L63" s="0" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M63" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="N63" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O63" s="12">
-        <f>'アイリス(1)'!V66</f>
-        <v/>
-      </c>
-      <c r="P63" s="0">
-        <f>O63=N63</f>
-        <v/>
-      </c>
+      <c r="I63" s="0" t="n"/>
+      <c r="J63" s="0" t="n"/>
+      <c r="K63" s="0" t="n"/>
+      <c r="L63" s="0" t="n"/>
+      <c r="M63" s="0" t="n"/>
+      <c r="N63" s="11" t="n"/>
+      <c r="O63" s="12" t="n"/>
+      <c r="P63" s="0" t="n"/>
     </row>
     <row r="64">
-      <c r="I64" s="0" t="n">
-        <v>114</v>
-      </c>
-      <c r="J64" s="0" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K64" s="0" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L64" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="M64" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="N64" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O64" s="12">
-        <f>'アイリス(1)'!V67</f>
-        <v/>
-      </c>
-      <c r="P64" s="0">
-        <f>O64=N64</f>
-        <v/>
-      </c>
+      <c r="I64" s="0" t="n"/>
+      <c r="J64" s="0" t="n"/>
+      <c r="K64" s="0" t="n"/>
+      <c r="L64" s="0" t="n"/>
+      <c r="M64" s="0" t="n"/>
+      <c r="N64" s="11" t="n"/>
+      <c r="O64" s="12" t="n"/>
+      <c r="P64" s="0" t="n"/>
     </row>
     <row r="65">
-      <c r="I65" s="0" t="n">
-        <v>118</v>
-      </c>
-      <c r="J65" s="0" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="K65" s="0" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L65" s="0" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M65" s="0" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N65" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O65" s="12">
-        <f>'アイリス(1)'!V68</f>
-        <v/>
-      </c>
-      <c r="P65" s="0">
-        <f>O65=N65</f>
-        <v/>
-      </c>
+      <c r="I65" s="0" t="n"/>
+      <c r="J65" s="0" t="n"/>
+      <c r="K65" s="0" t="n"/>
+      <c r="L65" s="0" t="n"/>
+      <c r="M65" s="0" t="n"/>
+      <c r="N65" s="11" t="n"/>
+      <c r="O65" s="12" t="n"/>
+      <c r="P65" s="0" t="n"/>
     </row>
     <row r="66">
-      <c r="I66" s="0" t="n">
-        <v>119</v>
-      </c>
-      <c r="J66" s="0" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="K66" s="0" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L66" s="0" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M66" s="0" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N66" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O66" s="12">
-        <f>'アイリス(1)'!V69</f>
-        <v/>
-      </c>
-      <c r="P66" s="0">
-        <f>O66=N66</f>
-        <v/>
-      </c>
+      <c r="I66" s="0" t="n"/>
+      <c r="J66" s="0" t="n"/>
+      <c r="K66" s="0" t="n"/>
+      <c r="L66" s="0" t="n"/>
+      <c r="M66" s="0" t="n"/>
+      <c r="N66" s="11" t="n"/>
+      <c r="O66" s="12" t="n"/>
+      <c r="P66" s="0" t="n"/>
     </row>
     <row r="67">
-      <c r="I67" s="0" t="n">
-        <v>124</v>
-      </c>
-      <c r="J67" s="0" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K67" s="0" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L67" s="0" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M67" s="0" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N67" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O67" s="12">
-        <f>'アイリス(1)'!V70</f>
-        <v/>
-      </c>
-      <c r="P67" s="0">
-        <f>O67=N67</f>
-        <v/>
-      </c>
+      <c r="I67" s="0" t="n"/>
+      <c r="J67" s="0" t="n"/>
+      <c r="K67" s="0" t="n"/>
+      <c r="L67" s="0" t="n"/>
+      <c r="M67" s="0" t="n"/>
+      <c r="N67" s="11" t="n"/>
+      <c r="O67" s="12" t="n"/>
+      <c r="P67" s="0" t="n"/>
     </row>
     <row r="68">
-      <c r="I68" s="0" t="n">
-        <v>125</v>
-      </c>
-      <c r="J68" s="0" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K68" s="0" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L68" s="0" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="M68" s="0" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N68" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O68" s="12">
-        <f>'アイリス(1)'!V71</f>
-        <v/>
-      </c>
-      <c r="P68" s="0">
-        <f>O68=N68</f>
-        <v/>
-      </c>
+      <c r="I68" s="0" t="n"/>
+      <c r="J68" s="0" t="n"/>
+      <c r="K68" s="0" t="n"/>
+      <c r="L68" s="0" t="n"/>
+      <c r="M68" s="0" t="n"/>
+      <c r="N68" s="11" t="n"/>
+      <c r="O68" s="12" t="n"/>
+      <c r="P68" s="0" t="n"/>
     </row>
     <row r="69">
-      <c r="I69" s="0" t="n">
-        <v>126</v>
-      </c>
-      <c r="J69" s="0" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K69" s="0" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L69" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="M69" s="0" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N69" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O69" s="12">
-        <f>'アイリス(1)'!V72</f>
-        <v/>
-      </c>
-      <c r="P69" s="0">
-        <f>O69=N69</f>
-        <v/>
-      </c>
+      <c r="I69" s="0" t="n"/>
+      <c r="J69" s="0" t="n"/>
+      <c r="K69" s="0" t="n"/>
+      <c r="L69" s="0" t="n"/>
+      <c r="M69" s="0" t="n"/>
+      <c r="N69" s="11" t="n"/>
+      <c r="O69" s="12" t="n"/>
+      <c r="P69" s="0" t="n"/>
     </row>
     <row r="70">
-      <c r="I70" s="0" t="n">
-        <v>128</v>
-      </c>
-      <c r="J70" s="0" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K70" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="L70" s="0" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M70" s="0" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N70" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O70" s="12">
-        <f>'アイリス(1)'!V73</f>
-        <v/>
-      </c>
-      <c r="P70" s="0">
-        <f>O70=N70</f>
-        <v/>
-      </c>
+      <c r="I70" s="0" t="n"/>
+      <c r="J70" s="0" t="n"/>
+      <c r="K70" s="0" t="n"/>
+      <c r="L70" s="0" t="n"/>
+      <c r="M70" s="0" t="n"/>
+      <c r="N70" s="11" t="n"/>
+      <c r="O70" s="12" t="n"/>
+      <c r="P70" s="0" t="n"/>
     </row>
     <row r="71">
-      <c r="I71" s="0" t="n">
-        <v>129</v>
-      </c>
-      <c r="J71" s="0" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K71" s="0" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L71" s="0" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M71" s="0" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N71" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O71" s="12">
-        <f>'アイリス(1)'!V74</f>
-        <v/>
-      </c>
-      <c r="P71" s="0">
-        <f>O71=N71</f>
-        <v/>
-      </c>
+      <c r="I71" s="0" t="n"/>
+      <c r="J71" s="0" t="n"/>
+      <c r="K71" s="0" t="n"/>
+      <c r="L71" s="0" t="n"/>
+      <c r="M71" s="0" t="n"/>
+      <c r="N71" s="11" t="n"/>
+      <c r="O71" s="12" t="n"/>
+      <c r="P71" s="0" t="n"/>
     </row>
     <row r="72">
-      <c r="I72" s="0" t="n">
-        <v>131</v>
-      </c>
-      <c r="J72" s="0" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K72" s="0" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L72" s="0" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M72" s="0" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N72" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O72" s="12">
-        <f>'アイリス(1)'!V75</f>
-        <v/>
-      </c>
-      <c r="P72" s="0">
-        <f>O72=N72</f>
-        <v/>
-      </c>
+      <c r="I72" s="0" t="n"/>
+      <c r="J72" s="0" t="n"/>
+      <c r="K72" s="0" t="n"/>
+      <c r="L72" s="0" t="n"/>
+      <c r="M72" s="0" t="n"/>
+      <c r="N72" s="11" t="n"/>
+      <c r="O72" s="12" t="n"/>
+      <c r="P72" s="0" t="n"/>
     </row>
     <row r="73">
-      <c r="I73" s="0" t="n">
-        <v>133</v>
-      </c>
-      <c r="J73" s="0" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K73" s="0" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L73" s="0" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M73" s="0" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N73" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O73" s="12">
-        <f>'アイリス(1)'!V76</f>
-        <v/>
-      </c>
-      <c r="P73" s="0">
-        <f>O73=N73</f>
-        <v/>
-      </c>
+      <c r="I73" s="0" t="n"/>
+      <c r="J73" s="0" t="n"/>
+      <c r="K73" s="0" t="n"/>
+      <c r="L73" s="0" t="n"/>
+      <c r="M73" s="0" t="n"/>
+      <c r="N73" s="11" t="n"/>
+      <c r="O73" s="12" t="n"/>
+      <c r="P73" s="0" t="n"/>
     </row>
     <row r="74">
-      <c r="I74" s="0" t="n">
-        <v>135</v>
-      </c>
-      <c r="J74" s="0" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K74" s="0" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L74" s="0" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M74" s="0" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N74" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O74" s="12">
-        <f>'アイリス(1)'!V77</f>
-        <v/>
-      </c>
-      <c r="P74" s="0">
-        <f>O74=N74</f>
-        <v/>
-      </c>
+      <c r="I74" s="0" t="n"/>
+      <c r="J74" s="0" t="n"/>
+      <c r="K74" s="0" t="n"/>
+      <c r="L74" s="0" t="n"/>
+      <c r="M74" s="0" t="n"/>
+      <c r="N74" s="11" t="n"/>
+      <c r="O74" s="12" t="n"/>
+      <c r="P74" s="0" t="n"/>
     </row>
     <row r="75">
-      <c r="I75" s="0" t="n">
-        <v>137</v>
-      </c>
-      <c r="J75" s="0" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K75" s="0" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L75" s="0" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M75" s="0" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N75" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O75" s="12">
-        <f>'アイリス(1)'!V78</f>
-        <v/>
-      </c>
-      <c r="P75" s="0">
-        <f>O75=N75</f>
-        <v/>
-      </c>
+      <c r="I75" s="0" t="n"/>
+      <c r="J75" s="0" t="n"/>
+      <c r="K75" s="0" t="n"/>
+      <c r="L75" s="0" t="n"/>
+      <c r="M75" s="0" t="n"/>
+      <c r="N75" s="11" t="n"/>
+      <c r="O75" s="12" t="n"/>
+      <c r="P75" s="0" t="n"/>
     </row>
     <row r="76">
-      <c r="I76" s="0" t="n">
-        <v>138</v>
-      </c>
-      <c r="J76" s="0" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K76" s="0" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L76" s="0" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M76" s="0" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N76" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O76" s="12">
-        <f>'アイリス(1)'!V79</f>
-        <v/>
-      </c>
-      <c r="P76" s="0">
-        <f>O76=N76</f>
-        <v/>
-      </c>
+      <c r="I76" s="0" t="n"/>
+      <c r="J76" s="0" t="n"/>
+      <c r="K76" s="0" t="n"/>
+      <c r="L76" s="0" t="n"/>
+      <c r="M76" s="0" t="n"/>
+      <c r="N76" s="11" t="n"/>
+      <c r="O76" s="12" t="n"/>
+      <c r="P76" s="0" t="n"/>
     </row>
     <row r="77">
-      <c r="I77" s="0" t="n">
-        <v>139</v>
-      </c>
-      <c r="J77" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="K77" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="L77" s="0" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M77" s="0" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N77" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O77" s="12">
-        <f>'アイリス(1)'!V80</f>
-        <v/>
-      </c>
-      <c r="P77" s="0">
-        <f>O77=N77</f>
-        <v/>
-      </c>
+      <c r="I77" s="0" t="n"/>
+      <c r="J77" s="0" t="n"/>
+      <c r="K77" s="0" t="n"/>
+      <c r="L77" s="0" t="n"/>
+      <c r="M77" s="0" t="n"/>
+      <c r="N77" s="11" t="n"/>
+      <c r="O77" s="12" t="n"/>
+      <c r="P77" s="0" t="n"/>
     </row>
     <row r="78">
-      <c r="I78" s="0" t="n">
-        <v>142</v>
-      </c>
-      <c r="J78" s="0" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K78" s="0" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L78" s="0" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M78" s="0" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N78" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O78" s="12">
-        <f>'アイリス(1)'!V81</f>
-        <v/>
-      </c>
-      <c r="P78" s="0">
-        <f>O78=N78</f>
-        <v/>
-      </c>
+      <c r="I78" s="0" t="n"/>
+      <c r="J78" s="0" t="n"/>
+      <c r="K78" s="0" t="n"/>
+      <c r="L78" s="0" t="n"/>
+      <c r="M78" s="0" t="n"/>
+      <c r="N78" s="11" t="n"/>
+      <c r="O78" s="12" t="n"/>
+      <c r="P78" s="0" t="n"/>
     </row>
     <row r="79">
-      <c r="I79" s="0" t="n">
-        <v>144</v>
-      </c>
-      <c r="J79" s="0" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K79" s="0" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L79" s="0" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M79" s="0" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N79" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O79" s="12">
-        <f>'アイリス(1)'!V82</f>
-        <v/>
-      </c>
-      <c r="P79" s="0">
-        <f>O79=N79</f>
-        <v/>
-      </c>
+      <c r="I79" s="0" t="n"/>
+      <c r="J79" s="0" t="n"/>
+      <c r="K79" s="0" t="n"/>
+      <c r="L79" s="0" t="n"/>
+      <c r="M79" s="0" t="n"/>
+      <c r="N79" s="11" t="n"/>
+      <c r="O79" s="12" t="n"/>
+      <c r="P79" s="0" t="n"/>
     </row>
     <row r="80">
-      <c r="I80" s="0" t="n">
-        <v>149</v>
-      </c>
-      <c r="J80" s="0" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K80" s="0" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L80" s="0" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M80" s="0" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N80" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O80" s="12">
-        <f>'アイリス(1)'!V83</f>
-        <v/>
-      </c>
-      <c r="P80" s="0">
-        <f>O80=N80</f>
-        <v/>
-      </c>
+      <c r="I80" s="0" t="n"/>
+      <c r="J80" s="0" t="n"/>
+      <c r="K80" s="0" t="n"/>
+      <c r="L80" s="0" t="n"/>
+      <c r="M80" s="0" t="n"/>
+      <c r="N80" s="11" t="n"/>
+      <c r="O80" s="12" t="n"/>
+      <c r="P80" s="0" t="n"/>
     </row>
     <row r="81">
-      <c r="I81" s="0" t="n">
-        <v>150</v>
-      </c>
-      <c r="J81" s="0" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K81" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="L81" s="0" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M81" s="0" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N81" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O81" s="12">
-        <f>'アイリス(1)'!V84</f>
-        <v/>
-      </c>
-      <c r="P81" s="0">
-        <f>O81=N81</f>
-        <v/>
-      </c>
+      <c r="I81" s="0" t="n"/>
+      <c r="J81" s="0" t="n"/>
+      <c r="K81" s="0" t="n"/>
+      <c r="L81" s="0" t="n"/>
+      <c r="M81" s="0" t="n"/>
+      <c r="N81" s="11" t="n"/>
+      <c r="O81" s="12" t="n"/>
+      <c r="P81" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12"/>
-  <cols>
-    <col width="22" customWidth="1" style="15" min="1" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1" s="15">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>アイリスデータでの再検証（別のランダム分割）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>目的：アイリス(2)シートの正解率100%は「出来すぎ」という注記があったため、</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>別のランダム分割（層化抽出・seed=2026）でも同程度の精度が出るかを確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>分割方法：品種ごとに7:3で層化抽出（元のiris1/iris2とは異なる組み合わせ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>学習データ：105件（setosa 35 / versicolor 35 / virginica 35）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>テストデータ：45件（setosa 15 / versicolor 15 / virginica 15、正解は分析時には使用せず）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>学習判別率（再代入精度）</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="n">
-        <v>0.9904761904761905</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>LOOCV交差検証精度</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="n">
-        <v>0.9904761904761905</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>テスト判別率（新規データの正解と比較）</t>
-        </is>
-      </c>
-      <c r="B13" s="0" t="n">
-        <v>0.9555555555555556</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>→ アイリス(2)は正解率100%だったが、別split（本シート）では95.6%。モデル自体は概ね妥当だが、100%は分割の巡り合わせが良かったためと考えられる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>テストデータ クロス集計（正解 × 予測）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>正解＼予測</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>1(setosa)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>2(versicolor)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>3(virginica)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B19" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="C19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="0" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="D20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="0" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="E21" s="0" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B22" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="C22" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="D22" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="E22" s="0" t="n">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>